--- a/data/trans_orig/P6708-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6708-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25498</t>
+          <t>26086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12745</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>19437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31417</t>
+          <t>31878</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56328</t>
+          <t>56519</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25807</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47889</t>
+          <t>48594</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63470</t>
+          <t>62289</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97011</t>
+          <t>97262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69536</t>
+          <t>67289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101267</t>
+          <t>100564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38917</t>
+          <t>38495</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64115</t>
+          <t>63214</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114846</t>
+          <t>110998</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155161</t>
+          <t>153523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146119</t>
+          <t>145254</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181135</t>
+          <t>181234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72940</t>
+          <t>75089</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103352</t>
+          <t>103705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229691</t>
+          <t>231597</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>275261</t>
+          <t>277170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,85%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30847</t>
+          <t>30947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29683</t>
+          <t>30708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26149</t>
+          <t>26048</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53532</t>
+          <t>54127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13594</t>
+          <t>13697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>33221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22716</t>
+          <t>22829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47082</t>
+          <t>47220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46306</t>
+          <t>47316</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74658</t>
+          <t>74466</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>24217</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46334</t>
+          <t>47307</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77390</t>
+          <t>78190</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112073</t>
+          <t>112525</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59332</t>
+          <t>61594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92641</t>
+          <t>92619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41477</t>
+          <t>41861</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68314</t>
+          <t>66746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111786</t>
+          <t>109661</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152154</t>
+          <t>151600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66313</t>
+          <t>64602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98480</t>
+          <t>97869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36726</t>
+          <t>36009</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61579</t>
+          <t>60812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109645</t>
+          <t>109073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151809</t>
+          <t>150668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>14943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20529</t>
+          <t>21130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25609</t>
+          <t>24717</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46301</t>
+          <t>45550</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74701</t>
+          <t>72155</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58073</t>
+          <t>57806</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>89992</t>
+          <t>87969</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>47120</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72482</t>
+          <t>74735</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>11473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>27439</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62908</t>
+          <t>64295</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94360</t>
+          <t>94681</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>122576</t>
+          <t>124103</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156868</t>
+          <t>158363</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62306</t>
+          <t>62606</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82193</t>
+          <t>82057</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>193188</t>
+          <t>192384</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>233158</t>
+          <t>231448</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36840</t>
+          <t>37926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65787</t>
+          <t>67353</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21563</t>
+          <t>21233</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42580</t>
+          <t>41352</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63609</t>
+          <t>64737</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98213</t>
+          <t>98408</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28921</t>
+          <t>30753</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55036</t>
+          <t>56014</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>24647</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48428</t>
+          <t>47312</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60821</t>
+          <t>60607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94989</t>
+          <t>96824</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75930</t>
+          <t>75100</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>109799</t>
+          <t>108765</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57652</t>
+          <t>57332</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87222</t>
+          <t>87579</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>142713</t>
+          <t>142890</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>188948</t>
+          <t>188824</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82482</t>
+          <t>82134</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117748</t>
+          <t>120980</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57112</t>
+          <t>57823</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87385</t>
+          <t>87195</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148241</t>
+          <t>146501</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>193845</t>
+          <t>193388</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>121516</t>
+          <t>120162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160593</t>
+          <t>160385</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>72921</t>
+          <t>75988</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>104565</t>
+          <t>107876</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>201149</t>
+          <t>202995</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>254911</t>
+          <t>257320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31316</t>
+          <t>32502</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39310</t>
+          <t>39618</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39201</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64949</t>
+          <t>65020</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15099</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32651</t>
+          <t>33180</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>11282</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>27091</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>30866</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54258</t>
+          <t>56636</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47382</t>
+          <t>46137</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>34053</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>58054</t>
+          <t>57005</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>64202</t>
+          <t>65576</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>97781</t>
+          <t>97094</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>20627</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40439</t>
+          <t>39179</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>22627</t>
+          <t>22714</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>43603</t>
+          <t>43576</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>49861</t>
+          <t>48106</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>77019</t>
+          <t>76849</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>30820</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>54234</t>
+          <t>53503</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39156</t>
+          <t>39519</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>65174</t>
+          <t>65769</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>76665</t>
+          <t>78371</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>109437</t>
+          <t>110592</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>87716</t>
+          <t>87866</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>128823</t>
+          <t>127920</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>72402</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>108590</t>
+          <t>109647</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>169705</t>
+          <t>172520</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>226599</t>
+          <t>225193</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>86457</t>
+          <t>85690</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>129721</t>
+          <t>126776</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>62846</t>
+          <t>61389</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>96407</t>
+          <t>96481</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>158530</t>
+          <t>157417</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>213647</t>
+          <t>211253</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>256732</t>
+          <t>256565</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>319024</t>
+          <t>319787</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>177376</t>
+          <t>176436</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>230250</t>
+          <t>230465</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>449964</t>
+          <t>451553</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>533697</t>
+          <t>535199</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>314598</t>
+          <t>313882</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>382109</t>
+          <t>379805</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>198330</t>
+          <t>201588</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>253894</t>
+          <t>253555</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>532542</t>
+          <t>529930</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>619180</t>
+          <t>616417</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>530960</t>
+          <t>531410</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>603346</t>
+          <t>606923</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>316610</t>
+          <t>318820</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>379608</t>
+          <t>380454</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>867141</t>
+          <t>870150</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>968930</t>
+          <t>969452</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12495</t>
+          <t>12252</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>19184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24691</t>
+          <t>25744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33921</t>
+          <t>33326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>19748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39015</t>
+          <t>39230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39635</t>
+          <t>39355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66675</t>
+          <t>66378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59516</t>
+          <t>59867</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89419</t>
+          <t>89276</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42258</t>
+          <t>40976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67097</t>
+          <t>66378</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>110191</t>
+          <t>109540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>150096</t>
+          <t>150044</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59830</t>
+          <t>60092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89738</t>
+          <t>92047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43864</t>
+          <t>42728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66919</t>
+          <t>69168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109789</t>
+          <t>108051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149829</t>
+          <t>146885</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85514</t>
+          <t>84968</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119788</t>
+          <t>119366</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53831</t>
+          <t>53861</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82797</t>
+          <t>81574</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149144</t>
+          <t>148940</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>191807</t>
+          <t>191232</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16358</t>
+          <t>15855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>36187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39492</t>
+          <t>41143</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38623</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66772</t>
+          <t>68862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40475</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25464</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48795</t>
+          <t>49087</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81798</t>
+          <t>84223</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60232</t>
+          <t>59687</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89403</t>
+          <t>89079</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30095</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53312</t>
+          <t>53426</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>97013</t>
+          <t>97805</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133677</t>
+          <t>133488</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46422</t>
+          <t>46963</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74486</t>
+          <t>75534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36814</t>
+          <t>35801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60886</t>
+          <t>61156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89634</t>
+          <t>91148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129832</t>
+          <t>127459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41881</t>
+          <t>43310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68618</t>
+          <t>70207</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25058</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48094</t>
+          <t>48685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>74415</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109045</t>
+          <t>110757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>16173</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>33634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46596</t>
+          <t>46468</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73887</t>
+          <t>72965</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>55630</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>87140</t>
+          <t>85250</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42423</t>
+          <t>41681</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68249</t>
+          <t>67762</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30703</t>
+          <t>30099</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61861</t>
+          <t>62181</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92095</t>
+          <t>92346</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59395</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87109</t>
+          <t>89257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23337</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39958</t>
+          <t>40425</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>88742</t>
+          <t>90084</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122013</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47026</t>
+          <t>44870</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74545</t>
+          <t>74672</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36830</t>
+          <t>36433</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64001</t>
+          <t>64340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88688</t>
+          <t>89764</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129947</t>
+          <t>132081</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67447</t>
+          <t>66922</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>101218</t>
+          <t>100961</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39646</t>
+          <t>40833</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66920</t>
+          <t>67071</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>114711</t>
+          <t>114402</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>158412</t>
+          <t>158469</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>115722</t>
+          <t>115645</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>155495</t>
+          <t>154535</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>93324</t>
+          <t>92017</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128200</t>
+          <t>126860</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>218607</t>
+          <t>218837</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>272900</t>
+          <t>271432</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85938</t>
+          <t>87416</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123995</t>
+          <t>123532</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69561</t>
+          <t>68791</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101927</t>
+          <t>101259</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166694</t>
+          <t>166281</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>217439</t>
+          <t>212567</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90465</t>
+          <t>87661</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>125769</t>
+          <t>124227</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>57982</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>88735</t>
+          <t>88315</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>155961</t>
+          <t>156220</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>206611</t>
+          <t>204396</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>28836</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51187</t>
+          <t>52229</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22052</t>
+          <t>21266</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42921</t>
+          <t>42550</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>54581</t>
+          <t>55137</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85754</t>
+          <t>86813</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26873</t>
+          <t>27599</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49827</t>
+          <t>50135</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28304</t>
+          <t>29311</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>52290</t>
+          <t>50459</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>60590</t>
+          <t>61792</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>92556</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41254</t>
+          <t>40362</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66795</t>
+          <t>67752</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>47928</t>
+          <t>47161</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>73563</t>
+          <t>71747</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>95504</t>
+          <t>94850</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>132477</t>
+          <t>130824</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18550</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>37914</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24368</t>
+          <t>22926</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>44318</t>
+          <t>44778</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>47175</t>
+          <t>48259</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>76286</t>
+          <t>76821</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>26063</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>50409</t>
+          <t>48907</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25100</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45916</t>
+          <t>47561</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>56780</t>
+          <t>57027</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>87600</t>
+          <t>87843</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>111470</t>
+          <t>115045</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>158323</t>
+          <t>159809</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>99287</t>
+          <t>101490</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>141357</t>
+          <t>142946</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>225385</t>
+          <t>225041</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>288282</t>
+          <t>289933</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>168945</t>
+          <t>169342</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>222879</t>
+          <t>225716</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>139517</t>
+          <t>136821</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>184809</t>
+          <t>180862</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>320752</t>
+          <t>317485</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>391493</t>
+          <t>388507</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>365109</t>
+          <t>362278</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>435417</t>
+          <t>432344</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>245510</t>
+          <t>245079</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>302755</t>
+          <t>302841</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>627715</t>
+          <t>624526</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>716367</t>
+          <t>713483</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>291051</t>
+          <t>290191</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>356502</t>
+          <t>353681</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>216255</t>
+          <t>216523</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>271213</t>
+          <t>269942</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>524217</t>
+          <t>522234</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>608084</t>
+          <t>607069</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>341227</t>
+          <t>343117</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>412121</t>
+          <t>406400</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>214970</t>
+          <t>217331</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>270710</t>
+          <t>272378</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>569609</t>
+          <t>573656</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>661158</t>
+          <t>664942</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -9377,32 +9377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>22102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9412,32 +9412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9447,32 +9447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23932</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33761</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -9490,32 +9490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9525,32 +9525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -9603,32 +9603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>19486</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28142</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9638,32 +9638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10439</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>23424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9673,32 +9673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>36177</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25145</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45462</t>
+          <t>48952</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -9716,32 +9716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>23413</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>15459</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29777</t>
+          <t>33561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9751,32 +9751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22644</t>
+          <t>23322</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16021</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30544</t>
+          <t>31318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9786,32 +9786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>42973</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32719</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>60704</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -9829,32 +9829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>38238</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23214</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43889</t>
+          <t>50608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9864,32 +9864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>29229</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>22231</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35185</t>
+          <t>38539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9899,32 +9899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>60904</t>
+          <t>67467</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47951</t>
+          <t>53998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75291</t>
+          <t>83646</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -9942,17 +9942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87609</t>
+          <t>98408</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87609</t>
+          <t>98408</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87609</t>
+          <t>98408</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9977,17 +9977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81149</t>
+          <t>86190</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81149</t>
+          <t>86190</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81149</t>
+          <t>86190</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10012,17 +10012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>168758</t>
+          <t>184598</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>168758</t>
+          <t>184598</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>168758</t>
+          <t>184598</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10059,32 +10059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16579</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>25581</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10094,32 +10094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>22561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10129,32 +10129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>32243</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38877</t>
+          <t>43604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -10172,32 +10172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10207,32 +10207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10242,32 +10242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>18794</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>28420</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -10285,32 +10285,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>21995</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13292</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29487</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10320,32 +10320,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17546</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24590</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10355,32 +10355,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>38381</t>
+          <t>40570</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28894</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48778</t>
+          <t>52062</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -10398,32 +10398,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19035</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10433,32 +10433,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10468,32 +10468,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19651</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>13757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29775</t>
+          <t>31630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -10511,32 +10511,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10546,32 +10546,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>20376</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10581,32 +10581,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>25552</t>
+          <t>27958</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>19300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37009</t>
+          <t>39187</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -10624,17 +10624,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10659,17 +10659,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61274</t>
+          <t>66528</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61274</t>
+          <t>66528</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61274</t>
+          <t>66528</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>130389</t>
+          <t>140906</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>130389</t>
+          <t>140906</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>130389</t>
+          <t>140906</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10776,32 +10776,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>810</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10811,32 +10811,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25756</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -10854,32 +10854,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53046</t>
+          <t>17745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -10899,12 +10899,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10924,32 +10924,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43199</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -10967,32 +10967,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24786</t>
+          <t>24737</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>132521</t>
+          <t>36359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>26044</t>
+          <t>26124</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103202</t>
+          <t>37395</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>37,51%</t>
         </is>
       </c>
     </row>
@@ -11080,32 +11080,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71113</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11115,32 +11115,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11150,32 +11150,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86776</t>
+          <t>30734</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -11193,32 +11193,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>261783</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67404</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>300010</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11228,32 +11228,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>14577</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11263,32 +11263,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>274166</t>
+          <t>35646</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99867</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>320662</t>
+          <t>46904</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>47,05%</t>
         </is>
       </c>
     </row>
@@ -11306,17 +11306,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11341,17 +11341,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11376,17 +11376,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11423,32 +11423,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30342</t>
+          <t>30708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11458,32 +11458,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>29155</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11493,32 +11493,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>45037</t>
+          <t>50079</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34653</t>
+          <t>38175</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57949</t>
+          <t>63916</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -11536,32 +11536,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>23140</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33146</t>
+          <t>35089</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11571,32 +11571,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11606,32 +11606,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>42087</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27696</t>
+          <t>30854</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52935</t>
+          <t>56457</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -11649,32 +11649,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33129</t>
+          <t>38011</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23335</t>
+          <t>27289</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44824</t>
+          <t>50643</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11684,32 +11684,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>31438</t>
+          <t>34033</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39347</t>
+          <t>44027</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11719,32 +11719,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>64568</t>
+          <t>72044</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51394</t>
+          <t>57568</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77753</t>
+          <t>85605</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -11762,32 +11762,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24645</t>
+          <t>25524</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>16866</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35528</t>
+          <t>37706</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11797,32 +11797,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>27627</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11832,32 +11832,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>43054</t>
+          <t>45637</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55077</t>
+          <t>59793</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -11875,32 +11875,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24490</t>
+          <t>26862</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35334</t>
+          <t>37595</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11910,32 +11910,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>20548</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11945,32 +11945,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>40781</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>28248</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>53325</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -11988,17 +11988,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12023,17 +12023,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>116166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>116166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>116166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12058,17 +12058,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>227891</t>
+          <t>250628</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>227891</t>
+          <t>250628</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>227891</t>
+          <t>250628</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12105,32 +12105,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>24238</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17636</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12140,32 +12140,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27428</t>
+          <t>34421</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12175,32 +12175,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>31040</t>
+          <t>50366</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>37635</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>65238</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -12218,32 +12218,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27948</t>
+          <t>31064</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12253,32 +12253,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>21610</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12288,32 +12288,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>34280</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19123</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>39920</t>
+          <t>46887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -12331,32 +12331,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>27099</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>17217</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35594</t>
+          <t>38714</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12366,32 +12366,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>25022</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32298</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12401,32 +12401,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>48653</t>
+          <t>54608</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>42939</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>63175</t>
+          <t>69013</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -12444,32 +12444,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>16886</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12479,32 +12479,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12514,32 +12514,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -12557,32 +12557,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>13142</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26079</t>
+          <t>30457</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12592,32 +12592,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12627,32 +12627,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>21494</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>33883</t>
+          <t>39682</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -12670,17 +12670,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12705,17 +12705,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>73235</t>
+          <t>87543</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>73235</t>
+          <t>87543</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>73235</t>
+          <t>87543</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12740,17 +12740,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>145614</t>
+          <t>181807</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>145614</t>
+          <t>181807</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>145614</t>
+          <t>181807</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12787,32 +12787,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>62842</t>
+          <t>78368</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>60457</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>108268</t>
+          <t>100965</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12822,32 +12822,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>70988</t>
+          <t>86193</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>59141</t>
+          <t>71035</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>85597</t>
+          <t>102061</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12857,32 +12857,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>133830</t>
+          <t>164561</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>64355</t>
+          <t>141038</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>187645</t>
+          <t>189580</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -12900,32 +12900,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>56129</t>
+          <t>61556</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>45760</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>96410</t>
+          <t>81283</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12935,32 +12935,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>45030</t>
+          <t>51863</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>34540</t>
+          <t>39655</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>57153</t>
+          <t>64114</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12970,32 +12970,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>101159</t>
+          <t>113419</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>45691</t>
+          <t>94029</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>144101</t>
+          <t>140134</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -13013,32 +13013,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>121237</t>
+          <t>131328</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>38737</t>
+          <t>111070</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>206293</t>
+          <t>156594</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13048,32 +13048,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>90764</t>
+          <t>98195</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>77288</t>
+          <t>83983</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>104518</t>
+          <t>113817</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13083,32 +13083,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>212001</t>
+          <t>229523</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>104178</t>
+          <t>201716</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>290898</t>
+          <t>256900</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -13126,32 +13126,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>75393</t>
+          <t>83429</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>67689</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>128258</t>
+          <t>102093</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13161,32 +13161,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>66874</t>
+          <t>69818</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>55475</t>
+          <t>56538</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>80179</t>
+          <t>83949</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13196,32 +13196,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>142267</t>
+          <t>153247</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>68605</t>
+          <t>133804</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>197106</t>
+          <t>176908</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -13239,32 +13239,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>347337</t>
+          <t>117588</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>150015</t>
+          <t>94538</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>556783</t>
+          <t>138970</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13274,32 +13274,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>71780</t>
+          <t>79286</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>58145</t>
+          <t>67163</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>84527</t>
+          <t>96157</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13309,32 +13309,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>419117</t>
+          <t>196874</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>222671</t>
+          <t>169151</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>709968</t>
+          <t>226231</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>662937</t>
+          <t>472269</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>662937</t>
+          <t>472269</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>662937</t>
+          <t>472269</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13387,17 +13387,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>345437</t>
+          <t>385355</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>345437</t>
+          <t>385355</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>345437</t>
+          <t>385355</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13422,17 +13422,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1008374</t>
+          <t>857624</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1008374</t>
+          <t>857624</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1008374</t>
+          <t>857624</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
